--- a/Kenya_Financial_Data_CLEAN.xlsx
+++ b/Kenya_Financial_Data_CLEAN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\project python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63D4B4C6-2127-4570-BA94-341FF2A1B4DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{194F1C8C-41B2-444B-952C-4EF02F6F9F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="500" yWindow="360" windowWidth="18330" windowHeight="10100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Indicator Name</t>
   </si>
@@ -133,6 +133,9 @@
   </si>
   <si>
     <t>lending rate</t>
+  </si>
+  <si>
+    <t>year to lookup</t>
   </si>
 </sst>
 </file>
@@ -1328,12 +1331,15 @@
         <v>11.6896167282259</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -1352,8 +1358,11 @@
       <c r="F19" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G19">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -1377,8 +1386,12 @@
         <f>INDEX($B$1:$P$1,MATCH(C20,B4:P4,0))</f>
         <v>2020</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G20">
+        <f>_xlfn.XLOOKUP(G19,B1:P1,B4:P4)</f>
+        <v>-0.27276632743881629</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -1402,8 +1415,16 @@
         <f>INDEX($B$1:$P$1,MATCH(D21,B7:P7,0))</f>
         <v>2024</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G21">
+        <f>_xlfn.XLOOKUP(G19,B1:P1,B7:P7)</f>
+        <v>11.8785758572124</v>
+      </c>
+      <c r="H21">
+        <f>_xlfn.XLOOKUP(MAX(B7:P7),B7:P7,B1:P1)</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -1427,8 +1448,16 @@
         <f>INDEX($B$1:$P$1,MATCH(D22,B9:P9,0))</f>
         <v>2011</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G22">
+        <f>_xlfn.XLOOKUP(G19,B1:P1,B9:P9)</f>
+        <v>5.4051620793339197</v>
+      </c>
+      <c r="H22">
+        <f>_xlfn.XLOOKUP(MIN(B9:P9),B9:P9,B1:P1)</f>
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -1453,7 +1482,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -1478,7 +1507,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>23</v>
       </c>
